--- a/forms/반 명단 엑셀 (이름으로 적기).xlsx
+++ b/forms/반 명단 엑셀 (이름으로 적기).xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMSUNG\OneDrive\바탕 화면\수업계획서 만들기\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMSUNG\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,108 +19,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+  <x:si>
+    <x:t>１호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화요일 3:40~4:40</x:t>
+  </x:si>
   <x:si>
     <x:t>화요일 2:10~3:20</x:t>
   </x:si>
   <x:si>
+    <x:t>수요일 4:00~6:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화요일 6:10~7:20</x:t>
+  </x:si>
+  <x:si>
     <x:t>화요일 7:20~8:40</x:t>
   </x:si>
   <x:si>
-    <x:t>화요일 6:10~7:20</x:t>
-  </x:si>
-  <x:si>
     <x:t>수요일 3:00~4:00</x:t>
   </x:si>
   <x:si>
-    <x:t>화요일 3:40~4:40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수요일 4:00~6:30</x:t>
+    <x:t>11월 4일,11일,18일,25일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11월 3일,10일,17일,24일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11월</x:t>
   </x:si>
   <x:si>
     <x:t>교과문학탐독１호</x:t>
   </x:si>
   <x:si>
-    <x:t>11월 4일,11일,18일,25일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11월 3일,10일,17일,24일</x:t>
+    <x:t>팀 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업월호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특이사항</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과학탐탐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세종대왕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세계사통사２호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몰입P2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신사임당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업요일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전봉준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>홍길동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이순신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안중근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이성계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유관순</x:t>
+  </x:si>
+  <x:si>
+    <x:t>２호</x:t>
   </x:si>
   <x:si>
     <x:t>이황</x:t>
   </x:si>
   <x:si>
-    <x:t>이성계</x:t>
+    <x:t xml:space="preserve">개인　</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">팀 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>이이</x:t>
   </x:si>
   <x:si>
     <x:t>이름</x:t>
   </x:si>
   <x:si>
-    <x:t>유관순</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">팀 </x:t>
+    <x:t>논리１</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강감찬</x:t>
   </x:si>
   <x:si>
     <x:t>팀</x:t>
   </x:si>
   <x:si>
-    <x:t>전봉준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강감찬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이순신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업요일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세종대왕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세계사통사２호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>팀 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신사임당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몰입P2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특이사항</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과학탐탐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>논리１</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>홍길동</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">개인　</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안중근</x:t>
+    <x:t>10월</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -167,7 +182,7 @@
       <x:patternFill patternType="gray125"/>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="5">
     <x:border>
       <x:left>
         <x:color rgb="ff000000"/>
@@ -193,6 +208,48 @@
         <x:color auto="1"/>
       </x:top>
       <x:bottom style="thin">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color auto="1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top>
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom>
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
@@ -205,7 +262,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -263,32 +320,6 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -297,6 +328,97 @@
       <mc:Fallback>
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -622,7 +744,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G15"/>
+  <x:dimension ref="A1:H15"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="3.48046875" style="1" bestFit="1" customWidth="1"/>
@@ -630,239 +752,270 @@
     <x:col min="3" max="3" width="9" style="1"/>
     <x:col min="4" max="4" width="22.59765625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="27.46875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="7" max="16384" width="9" style="1"/>
+    <x:col min="6" max="6" width="8.35546875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="27.46875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="16384" width="9" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
-      <x:c r="A2" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F2" s="5" t="s">
+      <x:c r="F2" s="7" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G2" s="4"/>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="5"/>
-      <x:c r="B3" s="5"/>
+      <x:c r="H2" s="4"/>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="6"/>
+      <x:c r="B3" s="6"/>
       <x:c r="C3" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="5"/>
-      <x:c r="E3" s="5"/>
-      <x:c r="F3" s="5"/>
-      <x:c r="G3" s="4"/>
-    </x:row>
-    <x:row r="4" spans="1:7">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="4"/>
+    </x:row>
+    <x:row r="4" spans="1:8">
       <x:c r="A4" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="E5" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H5" s="4"/>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="6"/>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6"/>
+      <x:c r="F6" s="10"/>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="4"/>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="6">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="s">
+      <x:c r="D7" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="5"/>
-      <x:c r="B6" s="5"/>
-      <x:c r="C6" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
-      <x:c r="G6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="5">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5"/>
+      <x:c r="H7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="6"/>
+      <x:c r="B8" s="6"/>
       <x:c r="C8" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="6"/>
-      <x:c r="G8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6"/>
+      <x:c r="F8" s="12"/>
+      <x:c r="G8" s="11"/>
+      <x:c r="H8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="6"/>
+      <x:c r="B9" s="6"/>
       <x:c r="C9" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D9" s="5"/>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="6"/>
+      <x:c r="E9" s="6"/>
+      <x:c r="F9" s="8"/>
+      <x:c r="G9" s="6"/>
+      <x:c r="H9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:8">
       <x:c r="A10" s="4">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G10" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H10" s="4"/>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="6">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="s">
+      <x:c r="E11" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G10" s="4"/>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="5">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="5"/>
-      <x:c r="B12" s="5"/>
+      <x:c r="H11" s="4"/>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="6"/>
+      <x:c r="B12" s="6"/>
       <x:c r="C12" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="4"/>
-    </x:row>
-    <x:row r="15" spans="6:6">
-      <x:c r="F15" s="7"/>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D12" s="6"/>
+      <x:c r="E12" s="6"/>
+      <x:c r="F12" s="8"/>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="4"/>
+    </x:row>
+    <x:row r="15" spans="7:7">
+      <x:c r="G15" s="5"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="20">
+  <x:mergeCells count="24">
     <x:mergeCell ref="A2:A3"/>
     <x:mergeCell ref="B2:B3"/>
     <x:mergeCell ref="D2:D3"/>
     <x:mergeCell ref="E2:E3"/>
     <x:mergeCell ref="F2:F3"/>
+    <x:mergeCell ref="G2:G3"/>
     <x:mergeCell ref="A5:A6"/>
     <x:mergeCell ref="B5:B6"/>
     <x:mergeCell ref="D5:D6"/>
     <x:mergeCell ref="E5:E6"/>
     <x:mergeCell ref="F5:F6"/>
+    <x:mergeCell ref="G5:G6"/>
     <x:mergeCell ref="A7:A9"/>
     <x:mergeCell ref="B7:B9"/>
     <x:mergeCell ref="D7:D9"/>
     <x:mergeCell ref="E7:E9"/>
     <x:mergeCell ref="F7:F9"/>
+    <x:mergeCell ref="G7:G9"/>
     <x:mergeCell ref="A11:A12"/>
     <x:mergeCell ref="B11:B12"/>
     <x:mergeCell ref="D11:D12"/>
     <x:mergeCell ref="E11:E12"/>
     <x:mergeCell ref="F11:F12"/>
+    <x:mergeCell ref="G11:G12"/>
   </x:mergeCells>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
